--- a/winnings-web/data/Winnings.xlsx
+++ b/winnings-web/data/Winnings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yagna\.openclaw\workspace\winnings-web\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16F2253D-CEEA-47D3-BA3A-D5BDBAD5D0C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78C2DFA9-F3DF-4638-B520-0F9341FBF07B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tennis Grand Slams" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,16 @@
     <sheet name="Cricket" sheetId="3" r:id="rId3"/>
     <sheet name="Golf" sheetId="4" r:id="rId4"/>
     <sheet name="About Us" sheetId="5" r:id="rId5"/>
-    <sheet name="All Sports Match Total Times" sheetId="6" r:id="rId6"/>
+    <sheet name="Chess" sheetId="7" r:id="rId6"/>
+    <sheet name="Soccer" sheetId="8" r:id="rId7"/>
+    <sheet name="All Sports Match Total Times" sheetId="6" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="532">
   <si>
     <t>Singles Mens and Womens</t>
   </si>
@@ -952,150 +954,39 @@
     <t>~$1.7K</t>
   </si>
   <si>
-    <t>ICC Event Prize Money Structures (Men’s &amp; Women’s)</t>
-  </si>
-  <si>
-    <t>Option</t>
-  </si>
-  <si>
-    <t>Tournament (Format)</t>
-  </si>
-  <si>
-    <t>Runner-Up</t>
-  </si>
-  <si>
-    <t>Other Key Prizes</t>
-  </si>
-  <si>
-    <t>ICC Men’s T20 World Cup 2024</t>
-  </si>
-  <si>
     <t>$2.45 M</t>
   </si>
   <si>
     <t>$1.28 M</t>
   </si>
   <si>
-    <t xml:space="preserve">SF: $787,500 each; 5th–8th: $382,500; 9th–12th: $247,500; 13th–20th: $225,000; $31,154 per match win (not including SF/Final) </t>
-  </si>
-  <si>
-    <t>ICC Men’s Cricket World Cup 2023 (ODI)</t>
-  </si>
-  <si>
     <t>$4 M</t>
   </si>
   <si>
     <t>$2 M</t>
   </si>
   <si>
-    <t xml:space="preserve">SF: $800,000 each; non-semis: $100,000 each; $40,000 per group win </t>
-  </si>
-  <si>
-    <t>ICC Men’s Champions Trophy 2025 (ODI)</t>
-  </si>
-  <si>
     <t>$2.24 M</t>
   </si>
   <si>
     <t>$1.12 M</t>
   </si>
   <si>
-    <t xml:space="preserve">SF: $560,000 each; 5th/6th: $350,000; 7th/8th: $140,000; participation: $125,000; group match win bonus ~$34,000 </t>
-  </si>
-  <si>
-    <t>ICC World Test Championship Final 2025</t>
-  </si>
-  <si>
     <t>$3.6 M</t>
   </si>
   <si>
     <t>$2.16 M</t>
   </si>
   <si>
-    <t xml:space="preserve">This is for the one-off final match of the 2023–2025 cycle. </t>
-  </si>
-  <si>
-    <t>ICC Women’s T20 World Cup 2024</t>
-  </si>
-  <si>
     <t>$2.34 M</t>
   </si>
   <si>
     <t>$1.17 M</t>
   </si>
   <si>
-    <t xml:space="preserve">SF: $675,000 each; Base participation $112,500; 3rd/4th in group $270,000; 5th/8th: sliding scale; $31,154 per match win </t>
-  </si>
-  <si>
-    <t>ICC Women’s Cricket World Cup 2025 (ODI)</t>
-  </si>
-  <si>
     <t>$4.48 M</t>
   </si>
   <si>
-    <t xml:space="preserve">SF: $1.12 M each; Base participate $250,000; 5th/6th: $700,000; 7th/8th: $280,000; group-stage win ~$34,314 </t>
-  </si>
-  <si>
-    <t>Prize Money for Domestic Tournaments (Team Rewards)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The BCCI revised prize money for the 2023–24 season and onward; the figures below show the total amounts awarded to teams based on tournament results. </t>
-  </si>
-  <si>
-    <t>Winners</t>
-  </si>
-  <si>
-    <t>Runners-Up</t>
-  </si>
-  <si>
-    <t>Losing Semi-Finalists</t>
-  </si>
-  <si>
-    <t>Ranji Trophy (Men)</t>
-  </si>
-  <si>
-    <t>₹5.00 crore</t>
-  </si>
-  <si>
-    <t>₹3.00 crore</t>
-  </si>
-  <si>
-    <t>₹1.00 crore</t>
-  </si>
-  <si>
-    <t>Irani Cup (Men)</t>
-  </si>
-  <si>
-    <t>₹50 lakh</t>
-  </si>
-  <si>
-    <t>₹25 lakh</t>
-  </si>
-  <si>
-    <t>–</t>
-  </si>
-  <si>
-    <t>Duleep Trophy (Men)</t>
-  </si>
-  <si>
-    <t>Vijay Hazare Trophy (Men)</t>
-  </si>
-  <si>
-    <t>Deodhar Trophy (Men)</t>
-  </si>
-  <si>
-    <t>₹40 lakh</t>
-  </si>
-  <si>
-    <t>₹20 lakh</t>
-  </si>
-  <si>
-    <t>Syed Mushtaq Ali Trophy (Men)</t>
-  </si>
-  <si>
-    <t>₹80 lakh</t>
-  </si>
-  <si>
     <t>Golf - Majors Men</t>
   </si>
   <si>
@@ -1505,13 +1396,251 @@
   </si>
   <si>
     <t>Time to complete a match</t>
+  </si>
+  <si>
+    <t>ICC Event Prize Money Structures - Men's</t>
+  </si>
+  <si>
+    <t>Position</t>
+  </si>
+  <si>
+    <t>ODI World Cup 2023</t>
+  </si>
+  <si>
+    <t>ODI Champions Trophy 2025</t>
+  </si>
+  <si>
+    <t>T20 World Cup 2024</t>
+  </si>
+  <si>
+    <t>World Test Championship Final 2025</t>
+  </si>
+  <si>
+    <t>Runner</t>
+  </si>
+  <si>
+    <t>Semi-Final</t>
+  </si>
+  <si>
+    <t>Group win</t>
+  </si>
+  <si>
+    <t>ICC Event Prize Money Structures - Women's</t>
+  </si>
+  <si>
+    <t>ODI Cricket World Cup 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$1.12 M </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3rd in group </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4th in group </t>
+  </si>
+  <si>
+    <t>Base participation</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Open (Men's)</t>
+  </si>
+  <si>
+    <t>World Chess Championship (Open)</t>
+  </si>
+  <si>
+    <t>Candidates (Open)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tata Steel</t>
+  </si>
+  <si>
+    <t>Norway Chess</t>
+  </si>
+  <si>
+    <t>Sinquefield Cup</t>
+  </si>
+  <si>
+    <t>Chennai GM</t>
+  </si>
+  <si>
+    <t>$1.2M–$1.8M</t>
+  </si>
+  <si>
+    <t>$100k–$120k</t>
+  </si>
+  <si>
+    <t>$800k–$1.2M</t>
+  </si>
+  <si>
+    <t>$80k–$100k</t>
+  </si>
+  <si>
+    <t>$70k–$90k</t>
+  </si>
+  <si>
+    <t>$60k–$80k</t>
+  </si>
+  <si>
+    <t>$50k–$60k</t>
+  </si>
+  <si>
+    <t>$40k–$50k</t>
+  </si>
+  <si>
+    <t>$30k–$40k</t>
+  </si>
+  <si>
+    <t>$20k–$30k</t>
+  </si>
+  <si>
+    <t>Women's</t>
+  </si>
+  <si>
+    <t>Women’s World Championship</t>
+  </si>
+  <si>
+    <t>Women’s Candidates</t>
+  </si>
+  <si>
+    <t>$300k–$600k</t>
+  </si>
+  <si>
+    <t>$200k–$400k</t>
+  </si>
+  <si>
+    <t>$25k–$30k</t>
+  </si>
+  <si>
+    <t>$20k–$25k</t>
+  </si>
+  <si>
+    <t>$15k–$20k</t>
+  </si>
+  <si>
+    <t>$10k–$15k</t>
+  </si>
+  <si>
+    <t>$5k–$10k</t>
+  </si>
+  <si>
+    <t>Both</t>
+  </si>
+  <si>
+    <t>Grand Swiss</t>
+  </si>
+  <si>
+    <t>Grand Prix</t>
+  </si>
+  <si>
+    <t>Qatar Masters</t>
+  </si>
+  <si>
+    <t>Dubai Open</t>
+  </si>
+  <si>
+    <t>Gibraltar</t>
+  </si>
+  <si>
+    <t>FIFA</t>
+  </si>
+  <si>
+    <t>FIFA World Cup 2026</t>
+  </si>
+  <si>
+    <t>FIFA Club World Cup</t>
+  </si>
+  <si>
+    <t>Champion</t>
+  </si>
+  <si>
+    <t>Runner‑up</t>
+  </si>
+  <si>
+    <t>3rd Place</t>
+  </si>
+  <si>
+    <t>4th Place</t>
+  </si>
+  <si>
+    <t>5th–8th</t>
+  </si>
+  <si>
+    <t>9th–16th</t>
+  </si>
+  <si>
+    <t>17th–32nd</t>
+  </si>
+  <si>
+    <t>33rd–48th</t>
+  </si>
+  <si>
+    <t>Participation</t>
+  </si>
+  <si>
+    <t>Continental</t>
+  </si>
+  <si>
+    <t>CAF Champions League</t>
+  </si>
+  <si>
+    <t>UEFA EURO 
+2024</t>
+  </si>
+  <si>
+    <t>Copa América 2024</t>
+  </si>
+  <si>
+    <t>CAF Champions League 
+(Africa)</t>
+  </si>
+  <si>
+    <t>Africa Cup of Nations (AFCON)</t>
+  </si>
+  <si>
+    <t>UEFA Europa League (2023/24)</t>
+  </si>
+  <si>
+    <t>CONMEBOL Copa Libertadores (2024)</t>
+  </si>
+  <si>
+    <t>UEFA Champions League</t>
+  </si>
+  <si>
+    <t>AFC Asian Cup 
+2023</t>
+  </si>
+  <si>
+    <t>Semi‑finalists</t>
+  </si>
+  <si>
+    <t>Quarter‑finalists</t>
+  </si>
+  <si>
+    <t>$900k </t>
+  </si>
+  <si>
+    <t>Group Stage Win</t>
+  </si>
+  <si>
+    <t>Group Stage Draw</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Position</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="164" formatCode="[$€-2]\ #,##0;[Red]\-[$€-2]\ #,##0"/>
+  </numFmts>
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1519,16 +1648,64 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1536,13 +1713,162 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1883,9 +2209,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1923,7 +2249,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>12</v>
       </c>
@@ -1958,7 +2284,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>16</v>
       </c>
@@ -1993,7 +2319,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>21</v>
       </c>
@@ -2028,7 +2354,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>26</v>
       </c>
@@ -2063,7 +2389,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>31</v>
       </c>
@@ -2098,7 +2424,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>37</v>
       </c>
@@ -2133,7 +2459,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>42</v>
       </c>
@@ -2153,7 +2479,7 @@
         <v>35260</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>44</v>
       </c>
@@ -2182,7 +2508,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>49</v>
       </c>
@@ -2208,7 +2534,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>54</v>
       </c>
@@ -2234,7 +2560,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>59</v>
       </c>
@@ -2260,7 +2586,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="J13" t="s">
         <v>64</v>
       </c>
@@ -2271,7 +2597,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>67</v>
       </c>
@@ -2303,7 +2629,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>12</v>
       </c>
@@ -2320,7 +2646,7 @@
         <v>680000</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>72</v>
       </c>
@@ -2337,7 +2663,7 @@
         <v>345000</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>74</v>
       </c>
@@ -2354,7 +2680,7 @@
         <v>174000</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>76</v>
       </c>
@@ -2371,7 +2697,7 @@
         <v>87500</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>78</v>
       </c>
@@ -2388,7 +2714,7 @@
         <v>43750</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>80</v>
       </c>
@@ -2405,7 +2731,7 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>44</v>
       </c>
@@ -2422,7 +2748,7 @@
         <v>16500</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>83</v>
       </c>
@@ -2445,7 +2771,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>12</v>
       </c>
@@ -2462,7 +2788,7 @@
         <v>135000</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>72</v>
       </c>
@@ -2479,7 +2805,7 @@
         <v>68000</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>74</v>
       </c>
@@ -2496,7 +2822,7 @@
         <v>34000</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>76</v>
       </c>
@@ -2513,7 +2839,7 @@
         <v>17500</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>31</v>
       </c>
@@ -2530,7 +2856,7 @@
         <v>9000</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>44</v>
       </c>
@@ -2555,14 +2881,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:X80"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>85</v>
       </c>
@@ -2597,7 +2923,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>95</v>
       </c>
@@ -2632,7 +2958,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>99</v>
       </c>
@@ -2661,7 +2987,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>107</v>
       </c>
@@ -2690,7 +3016,7 @@
         <v>24500</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>109</v>
       </c>
@@ -2719,7 +3045,7 @@
         <v>30895</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>110</v>
       </c>
@@ -2748,7 +3074,7 @@
         <v>30895</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>111</v>
       </c>
@@ -2777,7 +3103,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>113</v>
       </c>
@@ -2806,7 +3132,7 @@
         <v>35260</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>114</v>
       </c>
@@ -2841,7 +3167,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>117</v>
       </c>
@@ -2870,7 +3196,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="K12" t="s">
         <v>125</v>
       </c>
@@ -2878,17 +3204,17 @@
         <v>126</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="15" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>85</v>
       </c>
@@ -2914,7 +3240,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>129</v>
       </c>
@@ -2940,7 +3266,7 @@
         <v>25250</v>
       </c>
     </row>
-    <row r="17" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>130</v>
       </c>
@@ -2966,7 +3292,7 @@
         <v>22305</v>
       </c>
     </row>
-    <row r="18" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>131</v>
       </c>
@@ -2992,7 +3318,7 @@
         <v>21345</v>
       </c>
     </row>
-    <row r="19" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>132</v>
       </c>
@@ -3018,7 +3344,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="20" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>139</v>
       </c>
@@ -3044,7 +3370,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="21" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>146</v>
       </c>
@@ -3070,7 +3396,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="22" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>153</v>
       </c>
@@ -3096,7 +3422,7 @@
         <v>19670</v>
       </c>
     </row>
-    <row r="23" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>154</v>
       </c>
@@ -3122,7 +3448,7 @@
         <v>19680</v>
       </c>
     </row>
-    <row r="24" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>155</v>
       </c>
@@ -3142,12 +3468,12 @@
         <v>159</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="27" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>85</v>
       </c>
@@ -3179,7 +3505,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>95</v>
       </c>
@@ -3211,7 +3537,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="29" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>99</v>
       </c>
@@ -3243,7 +3569,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="30" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>107</v>
       </c>
@@ -3275,7 +3601,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="31" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>109</v>
       </c>
@@ -3307,7 +3633,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="32" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>110</v>
       </c>
@@ -3339,7 +3665,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="33" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>173</v>
       </c>
@@ -3371,7 +3697,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="34" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>113</v>
       </c>
@@ -3403,7 +3729,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="35" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>114</v>
       </c>
@@ -3435,7 +3761,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="36" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
         <v>117</v>
       </c>
@@ -3467,7 +3793,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="37" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
         <v>180</v>
       </c>
@@ -3493,7 +3819,7 @@
         <v>23500</v>
       </c>
     </row>
-    <row r="38" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
         <v>181</v>
       </c>
@@ -3519,12 +3845,12 @@
         <v>23450</v>
       </c>
     </row>
-    <row r="40" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="42" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
         <v>85</v>
       </c>
@@ -3550,69 +3876,69 @@
         <v>185</v>
       </c>
     </row>
-    <row r="43" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B43" s="1" t="s">
+    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B43" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="C43" s="1">
+      <c r="C43" s="8">
         <v>1415000</v>
       </c>
-      <c r="D43" s="1">
+      <c r="D43" s="8">
         <v>218930</v>
       </c>
-      <c r="E43" s="1">
+      <c r="E43" s="8">
         <v>134260</v>
       </c>
-      <c r="F43" s="1">
+      <c r="F43" s="8">
         <v>78425</v>
       </c>
-      <c r="G43" s="1">
+      <c r="G43" s="8">
         <v>38142</v>
       </c>
       <c r="H43" t="s">
         <v>187</v>
       </c>
-      <c r="I43" s="1" t="s">
+      <c r="I43" s="8" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="44" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
+    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
       <c r="H44" t="s">
         <v>189</v>
       </c>
-      <c r="I44" s="1"/>
-    </row>
-    <row r="45" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
+      <c r="I44" s="8"/>
+    </row>
+    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B45" s="8"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="8"/>
+      <c r="G45" s="8"/>
       <c r="H45" t="s">
         <v>190</v>
       </c>
-      <c r="I45" s="1"/>
-    </row>
-    <row r="46" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
+      <c r="I45" s="8"/>
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="8"/>
       <c r="H46" t="s">
         <v>191</v>
       </c>
-      <c r="I46" s="1"/>
-    </row>
-    <row r="47" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I46" s="8"/>
+    </row>
+    <row r="47" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
         <v>192</v>
       </c>
@@ -3638,7 +3964,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="48" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
         <v>195</v>
       </c>
@@ -3664,7 +3990,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="49" spans="2:24" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
         <v>197</v>
       </c>
@@ -3690,7 +4016,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="50" spans="2:24" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B50" t="s">
         <v>131</v>
       </c>
@@ -3716,7 +4042,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="51" spans="2:24" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
         <v>202</v>
       </c>
@@ -3742,112 +4068,112 @@
         <v>203</v>
       </c>
     </row>
-    <row r="52" spans="2:24" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B52" s="1" t="s">
+    <row r="52" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="B52" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="D52" s="1">
+      <c r="D52" s="8">
         <v>597000</v>
       </c>
-      <c r="E52" s="1">
+      <c r="E52" s="8">
         <v>351801</v>
       </c>
-      <c r="F52" s="1">
+      <c r="F52" s="8">
         <v>181400</v>
       </c>
-      <c r="G52" s="1">
+      <c r="G52" s="8">
         <v>83470</v>
       </c>
       <c r="H52" t="s">
         <v>206</v>
       </c>
-      <c r="I52" s="1" t="s">
+      <c r="I52" s="8" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="53" spans="2:24" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
-      <c r="D53" s="1"/>
-      <c r="E53" s="1"/>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
+    <row r="53" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="8"/>
       <c r="H53" t="s">
         <v>208</v>
       </c>
-      <c r="I53" s="1"/>
-    </row>
-    <row r="54" spans="2:24" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B54" s="1"/>
-      <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
-      <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
+      <c r="I53" s="8"/>
+    </row>
+    <row r="54" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="B54" s="8"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="8"/>
+      <c r="G54" s="8"/>
       <c r="H54" t="s">
         <v>209</v>
       </c>
-      <c r="I54" s="1"/>
-    </row>
-    <row r="55" spans="2:24" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B55" s="1" t="s">
+      <c r="I54" s="8"/>
+    </row>
+    <row r="55" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="B55" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="D55" s="1">
+      <c r="D55" s="8">
         <v>597000</v>
       </c>
-      <c r="E55" s="1">
+      <c r="E55" s="8">
         <v>351801</v>
       </c>
-      <c r="F55" s="1">
+      <c r="F55" s="8">
         <v>181400</v>
       </c>
-      <c r="G55" s="1">
+      <c r="G55" s="8">
         <v>83470</v>
       </c>
       <c r="H55" t="s">
         <v>212</v>
       </c>
-      <c r="I55" s="1" t="s">
+      <c r="I55" s="8" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="56" spans="2:24" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B56" s="1"/>
-      <c r="C56" s="1"/>
-      <c r="D56" s="1"/>
-      <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
+    <row r="56" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="B56" s="8"/>
+      <c r="C56" s="8"/>
+      <c r="D56" s="8"/>
+      <c r="E56" s="8"/>
+      <c r="F56" s="8"/>
+      <c r="G56" s="8"/>
       <c r="H56" t="s">
         <v>214</v>
       </c>
-      <c r="I56" s="1"/>
-    </row>
-    <row r="57" spans="2:24" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B57" s="1"/>
-      <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
+      <c r="I56" s="8"/>
+    </row>
+    <row r="57" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="B57" s="8"/>
+      <c r="C57" s="8"/>
+      <c r="D57" s="8"/>
+      <c r="E57" s="8"/>
+      <c r="F57" s="8"/>
+      <c r="G57" s="8"/>
       <c r="H57" t="s">
         <v>215</v>
       </c>
-      <c r="I57" s="1"/>
-    </row>
-    <row r="59" spans="2:24" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I57" s="8"/>
+    </row>
+    <row r="59" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B59" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="61" spans="2:24" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
         <v>85</v>
       </c>
@@ -3876,7 +4202,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="62" spans="2:24" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B62" t="s">
         <v>219</v>
       </c>
@@ -3935,7 +4261,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="63" spans="2:24" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
         <v>221</v>
       </c>
@@ -3985,7 +4311,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="64" spans="2:24" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B64" t="s">
         <v>228</v>
       </c>
@@ -4032,7 +4358,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="2:23" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B65" t="s">
         <v>230</v>
       </c>
@@ -4079,7 +4405,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="66" spans="2:23" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B66" t="s">
         <v>233</v>
       </c>
@@ -4126,7 +4452,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="67" spans="2:23" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B67" t="s">
         <v>235</v>
       </c>
@@ -4173,7 +4499,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="68" spans="2:23" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B68" t="s">
         <v>237</v>
       </c>
@@ -4220,7 +4546,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="69" spans="2:23" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B69" t="s">
         <v>240</v>
       </c>
@@ -4267,7 +4593,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="70" spans="2:23" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B70" t="s">
         <v>245</v>
       </c>
@@ -4320,7 +4646,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="71" spans="2:23" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B71" t="s">
         <v>225</v>
       </c>
@@ -4358,7 +4684,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="74" spans="2:23" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B74" t="s">
         <v>253</v>
       </c>
@@ -4381,7 +4707,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="75" spans="2:23" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B75" t="s">
         <v>254</v>
       </c>
@@ -4413,7 +4739,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="76" spans="2:23" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B76" t="s">
         <v>258</v>
       </c>
@@ -4436,7 +4762,7 @@
         <v>2975</v>
       </c>
     </row>
-    <row r="77" spans="2:23" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B77" t="s">
         <v>259</v>
       </c>
@@ -4459,7 +4785,7 @@
         <v>2975</v>
       </c>
     </row>
-    <row r="78" spans="2:23" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B78" t="s">
         <v>260</v>
       </c>
@@ -4482,7 +4808,7 @@
         <v>3110</v>
       </c>
     </row>
-    <row r="79" spans="2:23" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B79" t="s">
         <v>261</v>
       </c>
@@ -4505,7 +4831,7 @@
         <v>2975</v>
       </c>
     </row>
-    <row r="80" spans="2:23" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B80" t="s">
         <v>262</v>
       </c>
@@ -4561,15 +4887,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E48"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>264</v>
       </c>
@@ -4586,7 +4912,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>269</v>
       </c>
@@ -4603,7 +4929,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>274</v>
       </c>
@@ -4620,7 +4946,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>279</v>
       </c>
@@ -4637,7 +4963,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>284</v>
       </c>
@@ -4654,7 +4980,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>289</v>
       </c>
@@ -4671,7 +4997,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>294</v>
       </c>
@@ -4688,7 +5014,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>297</v>
       </c>
@@ -4705,7 +5031,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>302</v>
       </c>
@@ -4722,242 +5048,449 @@
         <v>306</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row r="13" spans="1:5" ht="18" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>456</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="E15" s="2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>461</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="B13" t="s">
-        <v>309</v>
-      </c>
-      <c r="C13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" t="s">
-        <v>310</v>
-      </c>
-      <c r="E13" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>1</v>
-      </c>
-      <c r="B14" t="s">
-        <v>312</v>
-      </c>
-      <c r="C14" t="s">
-        <v>313</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="E16" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="E14" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>2</v>
-      </c>
-      <c r="B15" t="s">
-        <v>316</v>
-      </c>
-      <c r="C15" t="s">
-        <v>317</v>
-      </c>
-      <c r="D15" t="s">
-        <v>318</v>
-      </c>
-      <c r="E15" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>3</v>
-      </c>
-      <c r="B16" t="s">
-        <v>320</v>
-      </c>
-      <c r="C16" t="s">
-        <v>321</v>
-      </c>
-      <c r="D16" t="s">
-        <v>322</v>
-      </c>
-      <c r="E16" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>4</v>
-      </c>
-      <c r="B17" t="s">
-        <v>324</v>
-      </c>
-      <c r="C17" t="s">
-        <v>325</v>
-      </c>
-      <c r="D17" t="s">
-        <v>326</v>
-      </c>
-      <c r="E17" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>462</v>
+      </c>
+      <c r="B17" s="4">
+        <v>800000</v>
+      </c>
+      <c r="C17" s="4">
+        <v>560000</v>
+      </c>
+      <c r="D17" s="4">
+        <v>787500</v>
+      </c>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>5</v>
       </c>
-      <c r="B18" t="s">
-        <v>328</v>
-      </c>
-      <c r="C18" t="s">
-        <v>329</v>
-      </c>
-      <c r="D18" t="s">
-        <v>330</v>
-      </c>
-      <c r="E18" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B18" s="4">
+        <v>100000</v>
+      </c>
+      <c r="C18" s="4">
+        <v>350000</v>
+      </c>
+      <c r="D18" s="4">
+        <v>382500</v>
+      </c>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>6</v>
       </c>
-      <c r="B19" t="s">
-        <v>332</v>
-      </c>
-      <c r="C19" t="s">
-        <v>333</v>
-      </c>
-      <c r="D19" t="s">
-        <v>321</v>
-      </c>
-      <c r="E19" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B25" t="s">
-        <v>85</v>
-      </c>
-      <c r="C25" t="s">
-        <v>337</v>
-      </c>
-      <c r="D25" t="s">
-        <v>338</v>
-      </c>
-      <c r="E25" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B26" t="s">
-        <v>340</v>
-      </c>
-      <c r="C26" t="s">
-        <v>341</v>
-      </c>
-      <c r="D26" t="s">
-        <v>342</v>
-      </c>
-      <c r="E26" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B27" t="s">
-        <v>344</v>
-      </c>
-      <c r="C27" t="s">
-        <v>345</v>
-      </c>
-      <c r="D27" t="s">
-        <v>346</v>
-      </c>
-      <c r="E27" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B28" t="s">
-        <v>348</v>
-      </c>
-      <c r="C28" t="s">
-        <v>343</v>
-      </c>
-      <c r="D28" t="s">
-        <v>345</v>
-      </c>
-      <c r="E28" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B29" t="s">
-        <v>349</v>
-      </c>
-      <c r="C29" t="s">
-        <v>343</v>
-      </c>
-      <c r="D29" t="s">
-        <v>345</v>
-      </c>
-      <c r="E29" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B30" t="s">
-        <v>350</v>
-      </c>
-      <c r="C30" t="s">
-        <v>351</v>
-      </c>
-      <c r="D30" t="s">
-        <v>352</v>
-      </c>
-      <c r="E30" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B31" t="s">
-        <v>353</v>
-      </c>
-      <c r="C31" t="s">
-        <v>354</v>
-      </c>
-      <c r="D31" t="s">
-        <v>351</v>
-      </c>
-      <c r="E31" t="s">
-        <v>347</v>
-      </c>
+      <c r="B19" s="4">
+        <v>100000</v>
+      </c>
+      <c r="C19" s="4">
+        <v>350000</v>
+      </c>
+      <c r="D19" s="4">
+        <v>382500</v>
+      </c>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>7</v>
+      </c>
+      <c r="B20" s="4">
+        <v>100000</v>
+      </c>
+      <c r="C20" s="4">
+        <v>140000</v>
+      </c>
+      <c r="D20" s="4">
+        <v>382500</v>
+      </c>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>8</v>
+      </c>
+      <c r="B21" s="4">
+        <v>100000</v>
+      </c>
+      <c r="C21" s="4">
+        <v>140000</v>
+      </c>
+      <c r="D21" s="4">
+        <v>382500</v>
+      </c>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>9</v>
+      </c>
+      <c r="C22" s="4">
+        <v>125000</v>
+      </c>
+      <c r="D22" s="4">
+        <v>247500</v>
+      </c>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>10</v>
+      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" s="4">
+        <v>125000</v>
+      </c>
+      <c r="D23" s="4">
+        <v>247500</v>
+      </c>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>11</v>
+      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" s="4">
+        <v>125000</v>
+      </c>
+      <c r="D24" s="4">
+        <v>247500</v>
+      </c>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>12</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" s="4">
+        <v>125000</v>
+      </c>
+      <c r="D25" s="4">
+        <v>247500</v>
+      </c>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>13</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="D26" s="4">
+        <v>225000</v>
+      </c>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>14</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="4">
+        <v>225000</v>
+      </c>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>15</v>
+      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="4">
+        <v>225000</v>
+      </c>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>16</v>
+      </c>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="4">
+        <v>225000</v>
+      </c>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>17</v>
+      </c>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="4">
+        <v>225000</v>
+      </c>
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>18</v>
+      </c>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="4">
+        <v>225000</v>
+      </c>
+      <c r="E31" s="2"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>19</v>
+      </c>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="4">
+        <v>225000</v>
+      </c>
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>20</v>
+      </c>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="4">
+        <v>225000</v>
+      </c>
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>463</v>
+      </c>
+      <c r="B34" s="4">
+        <v>40000</v>
+      </c>
+      <c r="C34" s="4">
+        <v>34000</v>
+      </c>
+      <c r="D34" s="4">
+        <v>31154</v>
+      </c>
+      <c r="E34" s="2"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+    </row>
+    <row r="36" spans="1:5" ht="18" x14ac:dyDescent="0.35">
+      <c r="A36" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>456</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>461</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>462</v>
+      </c>
+      <c r="B40" s="4">
+        <v>675000</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>5</v>
+      </c>
+      <c r="B41" s="2"/>
+      <c r="C41" s="4">
+        <v>700000</v>
+      </c>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>6</v>
+      </c>
+      <c r="B42" s="2"/>
+      <c r="C42" s="4">
+        <v>700000</v>
+      </c>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>7</v>
+      </c>
+      <c r="B43" s="2"/>
+      <c r="C43" s="4">
+        <v>280000</v>
+      </c>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>8</v>
+      </c>
+      <c r="B44" s="2"/>
+      <c r="C44" s="4">
+        <v>280000</v>
+      </c>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>467</v>
+      </c>
+      <c r="B45" s="4">
+        <v>270000</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>468</v>
+      </c>
+      <c r="B46" s="4">
+        <v>270000</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>463</v>
+      </c>
+      <c r="B47" s="4">
+        <v>31154</v>
+      </c>
+      <c r="C47" s="4">
+        <v>34314</v>
+      </c>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>469</v>
+      </c>
+      <c r="B48" s="4">
+        <v>112500</v>
+      </c>
+      <c r="C48" s="4">
+        <v>250000</v>
+      </c>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:E31" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:E11" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4965,31 +5498,31 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J170"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>356</v>
+        <v>319</v>
       </c>
       <c r="B2" t="s">
-        <v>357</v>
+        <v>320</v>
       </c>
       <c r="C2" t="s">
-        <v>358</v>
+        <v>321</v>
       </c>
       <c r="D2" t="s">
-        <v>359</v>
+        <v>322</v>
       </c>
       <c r="E2" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5006,7 +5539,7 @@
         <v>3100000</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -5023,7 +5556,7 @@
         <v>1759000</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -5040,7 +5573,7 @@
         <v>1128000</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -5057,7 +5590,7 @@
         <v>876000</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -5074,7 +5607,7 @@
         <v>705000</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -5091,7 +5624,7 @@
         <v>611000</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -5108,7 +5641,7 @@
         <v>525000</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -5125,7 +5658,7 @@
         <v>442500</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -5142,7 +5675,7 @@
         <v>388000</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -5159,7 +5692,7 @@
         <v>350600</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
@@ -5176,7 +5709,7 @@
         <v>319200</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
@@ -5193,7 +5726,7 @@
         <v>282800</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
@@ -5210,7 +5743,7 @@
         <v>266000</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
@@ -5227,7 +5760,7 @@
         <v>249000</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>15</v>
       </c>
@@ -5244,7 +5777,7 @@
         <v>231000</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>
@@ -5261,7 +5794,7 @@
         <v>212700</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>17</v>
       </c>
@@ -5278,7 +5811,7 @@
         <v>202400</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>18</v>
       </c>
@@ -5295,7 +5828,7 @@
         <v>193000</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>19</v>
       </c>
@@ -5312,7 +5845,7 @@
         <v>184900</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>20</v>
       </c>
@@ -5329,7 +5862,7 @@
         <v>176200</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>21</v>
       </c>
@@ -5346,7 +5879,7 @@
         <v>168000</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>22</v>
       </c>
@@ -5363,7 +5896,7 @@
         <v>159600</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>23</v>
       </c>
@@ -5380,7 +5913,7 @@
         <v>151000</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>24</v>
       </c>
@@ -5397,7 +5930,7 @@
         <v>142600</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>25</v>
       </c>
@@ -5414,7 +5947,7 @@
         <v>137800</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26</v>
       </c>
@@ -5431,7 +5964,7 @@
         <v>131800</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>27</v>
       </c>
@@ -5448,7 +5981,7 @@
         <v>127000</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>28</v>
       </c>
@@ -5465,7 +5998,7 @@
         <v>122600</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>29</v>
       </c>
@@ -5482,7 +6015,7 @@
         <v>117300</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>30</v>
       </c>
@@ -5499,7 +6032,7 @@
         <v>111200</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>31</v>
       </c>
@@ -5516,7 +6049,7 @@
         <v>107600</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>32</v>
       </c>
@@ -5533,7 +6066,7 @@
         <v>102100</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>33</v>
       </c>
@@ -5550,7 +6083,7 @@
         <v>98500</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>34</v>
       </c>
@@ -5567,7 +6100,7 @@
         <v>95700</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>35</v>
       </c>
@@ -5584,7 +6117,7 @@
         <v>92400</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>36</v>
       </c>
@@ -5601,7 +6134,7 @@
         <v>88700</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>37</v>
       </c>
@@ -5618,7 +6151,7 @@
         <v>84600</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>38</v>
       </c>
@@ -5635,7 +6168,7 @@
         <v>80300</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>39</v>
       </c>
@@ -5652,7 +6185,7 @@
         <v>77400</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>40</v>
       </c>
@@ -5669,7 +6202,7 @@
         <v>74900</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>41</v>
       </c>
@@ -5686,7 +6219,7 @@
         <v>71800</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>42</v>
       </c>
@@ -5703,12 +6236,12 @@
         <v>68300</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="C45">
         <v>75047</v>
@@ -5720,12 +6253,12 @@
         <v>65200</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="C46">
         <v>70658</v>
@@ -5737,12 +6270,12 @@
         <v>61500</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="C47">
         <v>66269</v>
@@ -5754,12 +6287,12 @@
         <v>58000</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="C48">
         <v>62320</v>
@@ -5771,12 +6304,12 @@
         <v>55000</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="C49">
         <v>58370</v>
@@ -5788,12 +6321,12 @@
         <v>52800</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="C50">
         <v>54639</v>
@@ -5805,12 +6338,12 @@
         <v>50700</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="C51">
         <v>52445</v>
@@ -5822,12 +6355,12 @@
         <v>48400</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="C52">
         <v>50251</v>
@@ -5839,12 +6372,12 @@
         <v>47200</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="C53">
         <v>48934</v>
@@ -5856,12 +6389,12 @@
         <v>46200</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="C54">
         <v>47837</v>
@@ -5873,12 +6406,12 @@
         <v>45400</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="C55">
         <v>46959</v>
@@ -5890,12 +6423,12 @@
         <v>44700</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="C56">
         <v>46520</v>
@@ -5907,12 +6440,12 @@
         <v>44000</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="C57">
         <v>46081</v>
@@ -5924,12 +6457,12 @@
         <v>43300</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="C58">
         <v>45642</v>
@@ -5941,12 +6474,12 @@
         <v>42700</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="C59">
         <v>45203</v>
@@ -5958,12 +6491,12 @@
         <v>42300</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="C60">
         <v>44765</v>
@@ -5975,12 +6508,12 @@
         <v>42000</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="C61">
         <v>44326</v>
@@ -5992,12 +6525,12 @@
         <v>41700</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="C62">
         <v>43887</v>
@@ -6009,12 +6542,12 @@
         <v>41400</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="C63">
         <v>43448</v>
@@ -6026,12 +6559,12 @@
         <v>41200</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="C64">
         <v>43009</v>
@@ -6043,12 +6576,12 @@
         <v>41000</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="C65">
         <v>42570</v>
@@ -6060,12 +6593,12 @@
         <v>40800</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="C66">
         <v>42131</v>
@@ -6077,12 +6610,12 @@
         <v>40600</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="C67">
         <v>41692</v>
@@ -6094,12 +6627,12 @@
         <v>40300</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="C68">
         <v>41254</v>
@@ -6111,15 +6644,15 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="C69" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="D69">
         <v>25290</v>
@@ -6128,15 +6661,15 @@
         <v>39700</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="C70" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="D70">
         <v>24920</v>
@@ -6145,15 +6678,15 @@
         <v>39400</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="C71" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="D71">
         <v>24570</v>
@@ -6162,15 +6695,15 @@
         <v>39100</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="C72" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="D72">
         <v>24240</v>
@@ -6179,754 +6712,754 @@
         <v>38900</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="C73" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="D73">
         <v>23940</v>
       </c>
       <c r="E73" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="C74" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="D74">
         <v>23740</v>
       </c>
       <c r="E74" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="C75" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="D75">
         <v>23570</v>
       </c>
       <c r="E75" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="C76" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="D76">
         <v>23420</v>
       </c>
       <c r="E76" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>356</v>
+        <v>319</v>
       </c>
       <c r="B79" t="s">
-        <v>363</v>
+        <v>326</v>
       </c>
       <c r="C79" t="s">
-        <v>364</v>
+        <v>327</v>
       </c>
       <c r="D79" t="s">
-        <v>365</v>
+        <v>328</v>
       </c>
       <c r="E79" t="s">
-        <v>366</v>
+        <v>329</v>
       </c>
       <c r="F79" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>368</v>
+        <v>331</v>
       </c>
       <c r="B81" t="s">
-        <v>369</v>
+        <v>332</v>
       </c>
       <c r="C81" t="s">
-        <v>370</v>
+        <v>333</v>
       </c>
       <c r="D81" t="s">
-        <v>371</v>
+        <v>334</v>
       </c>
       <c r="E81" t="s">
-        <v>372</v>
+        <v>335</v>
       </c>
       <c r="F81">
         <v>1200000</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
+        <v>336</v>
+      </c>
+      <c r="B82" t="s">
+        <v>337</v>
+      </c>
+      <c r="C82" t="s">
+        <v>338</v>
+      </c>
+      <c r="D82" t="s">
+        <v>339</v>
+      </c>
+      <c r="E82" t="s">
+        <v>340</v>
+      </c>
+      <c r="F82" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>342</v>
+      </c>
+      <c r="B84" t="s">
+        <v>337</v>
+      </c>
+      <c r="C84" t="s">
+        <v>338</v>
+      </c>
+      <c r="D84" t="s">
+        <v>339</v>
+      </c>
+      <c r="E84" t="s">
+        <v>340</v>
+      </c>
+      <c r="F84" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>344</v>
+      </c>
+      <c r="B86" t="s">
+        <v>345</v>
+      </c>
+      <c r="C86" t="s">
+        <v>346</v>
+      </c>
+      <c r="D86" t="s">
+        <v>339</v>
+      </c>
+      <c r="E86" t="s">
+        <v>347</v>
+      </c>
+      <c r="F86" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>349</v>
+      </c>
+      <c r="B88" t="s">
+        <v>345</v>
+      </c>
+      <c r="C88" t="s">
+        <v>350</v>
+      </c>
+      <c r="D88" t="s">
+        <v>339</v>
+      </c>
+      <c r="E88" t="s">
+        <v>347</v>
+      </c>
+      <c r="F88" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>351</v>
+      </c>
+      <c r="B90" t="s">
+        <v>352</v>
+      </c>
+      <c r="C90" t="s">
+        <v>353</v>
+      </c>
+      <c r="D90" t="s">
+        <v>354</v>
+      </c>
+      <c r="E90" t="s">
+        <v>355</v>
+      </c>
+      <c r="F90" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>357</v>
+      </c>
+      <c r="B92" t="s">
+        <v>352</v>
+      </c>
+      <c r="C92" t="s">
+        <v>353</v>
+      </c>
+      <c r="D92" t="s">
+        <v>354</v>
+      </c>
+      <c r="E92" t="s">
+        <v>355</v>
+      </c>
+      <c r="F92" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>359</v>
+      </c>
+      <c r="B94" t="s">
+        <v>360</v>
+      </c>
+      <c r="C94" t="s">
+        <v>361</v>
+      </c>
+      <c r="D94" t="s">
+        <v>354</v>
+      </c>
+      <c r="E94" t="s">
+        <v>362</v>
+      </c>
+      <c r="F94" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>364</v>
+      </c>
+      <c r="B96" t="s">
+        <v>360</v>
+      </c>
+      <c r="C96" t="s">
+        <v>361</v>
+      </c>
+      <c r="D96" t="s">
+        <v>365</v>
+      </c>
+      <c r="E96" t="s">
+        <v>362</v>
+      </c>
+      <c r="F96" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>367</v>
+      </c>
+      <c r="B98" t="s">
+        <v>360</v>
+      </c>
+      <c r="C98" t="s">
+        <v>368</v>
+      </c>
+      <c r="D98" t="s">
+        <v>365</v>
+      </c>
+      <c r="E98" t="s">
+        <v>369</v>
+      </c>
+      <c r="F98" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>371</v>
+      </c>
+      <c r="B100" t="s">
+        <v>372</v>
+      </c>
+      <c r="C100" t="s">
         <v>373</v>
       </c>
-      <c r="B82" t="s">
+      <c r="D100" t="s">
         <v>374</v>
       </c>
-      <c r="C82" t="s">
+      <c r="E100" t="s">
         <v>375</v>
       </c>
-      <c r="D82" t="s">
+      <c r="F100" t="s">
         <v>376</v>
       </c>
-      <c r="E82" t="s">
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
         <v>377</v>
       </c>
-      <c r="F82" t="s">
+      <c r="B102" t="s">
+        <v>372</v>
+      </c>
+      <c r="C102" t="s">
+        <v>373</v>
+      </c>
+      <c r="D102" t="s">
+        <v>374</v>
+      </c>
+      <c r="E102" t="s">
+        <v>375</v>
+      </c>
+      <c r="F102" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
         <v>379</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B104" t="s">
+        <v>380</v>
+      </c>
+      <c r="C104" t="s">
+        <v>380</v>
+      </c>
+      <c r="D104" t="s">
+        <v>380</v>
+      </c>
+      <c r="E104" t="s">
+        <v>380</v>
+      </c>
+      <c r="F104" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>382</v>
+      </c>
+      <c r="B106" t="s">
+        <v>383</v>
+      </c>
+      <c r="C106" t="s">
+        <v>373</v>
+      </c>
+      <c r="D106" t="s">
         <v>374</v>
       </c>
-      <c r="C84" t="s">
-        <v>375</v>
-      </c>
-      <c r="D84" t="s">
-        <v>376</v>
-      </c>
-      <c r="E84" t="s">
-        <v>377</v>
-      </c>
-      <c r="F84" t="s">
+      <c r="E106" t="s">
+        <v>384</v>
+      </c>
+      <c r="F106" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>386</v>
+      </c>
+      <c r="B108" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="86" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
-        <v>381</v>
-      </c>
-      <c r="B86" t="s">
-        <v>382</v>
-      </c>
-      <c r="C86" t="s">
-        <v>383</v>
-      </c>
-      <c r="D86" t="s">
-        <v>376</v>
-      </c>
-      <c r="E86" t="s">
-        <v>384</v>
-      </c>
-      <c r="F86" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
-        <v>386</v>
-      </c>
-      <c r="B88" t="s">
-        <v>382</v>
-      </c>
-      <c r="C88" t="s">
+      <c r="C108" t="s">
+        <v>380</v>
+      </c>
+      <c r="D108" t="s">
+        <v>380</v>
+      </c>
+      <c r="E108" t="s">
+        <v>380</v>
+      </c>
+      <c r="F108" t="s">
         <v>387</v>
       </c>
-      <c r="D88" t="s">
-        <v>376</v>
-      </c>
-      <c r="E88" t="s">
-        <v>384</v>
-      </c>
-      <c r="F88" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
         <v>388</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B110" t="s">
+        <v>380</v>
+      </c>
+      <c r="C110" t="s">
+        <v>380</v>
+      </c>
+      <c r="D110" t="s">
+        <v>380</v>
+      </c>
+      <c r="E110" t="s">
+        <v>380</v>
+      </c>
+      <c r="F110" t="s">
         <v>389</v>
       </c>
-      <c r="C90" t="s">
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
         <v>390</v>
       </c>
-      <c r="D90" t="s">
+      <c r="B112" t="s">
+        <v>380</v>
+      </c>
+      <c r="C112" t="s">
+        <v>380</v>
+      </c>
+      <c r="D112" t="s">
+        <v>380</v>
+      </c>
+      <c r="E112" t="s">
+        <v>380</v>
+      </c>
+      <c r="F112" t="s">
         <v>391</v>
       </c>
-      <c r="E90" t="s">
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
         <v>392</v>
       </c>
-      <c r="F90" t="s">
+      <c r="B114" t="s">
+        <v>380</v>
+      </c>
+      <c r="C114" t="s">
+        <v>380</v>
+      </c>
+      <c r="D114" t="s">
+        <v>380</v>
+      </c>
+      <c r="E114" t="s">
+        <v>380</v>
+      </c>
+      <c r="F114" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="92" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
         <v>394</v>
       </c>
-      <c r="B92" t="s">
-        <v>389</v>
-      </c>
-      <c r="C92" t="s">
-        <v>390</v>
-      </c>
-      <c r="D92" t="s">
-        <v>391</v>
-      </c>
-      <c r="E92" t="s">
-        <v>392</v>
-      </c>
-      <c r="F92" t="s">
+      <c r="B116" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="94" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
+      <c r="C116" t="s">
+        <v>369</v>
+      </c>
+      <c r="D116" t="s">
         <v>396</v>
       </c>
-      <c r="B94" t="s">
+      <c r="E116" t="s">
         <v>397</v>
       </c>
-      <c r="C94" t="s">
+      <c r="F116" t="s">
         <v>398</v>
       </c>
-      <c r="D94" t="s">
-        <v>391</v>
-      </c>
-      <c r="E94" t="s">
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
         <v>399</v>
       </c>
-      <c r="F94" t="s">
+      <c r="B118" t="s">
+        <v>369</v>
+      </c>
+      <c r="C118" t="s">
+        <v>369</v>
+      </c>
+      <c r="D118" t="s">
+        <v>396</v>
+      </c>
+      <c r="E118" t="s">
+        <v>369</v>
+      </c>
+      <c r="F118" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
         <v>401</v>
       </c>
-      <c r="B96" t="s">
-        <v>397</v>
-      </c>
-      <c r="C96" t="s">
-        <v>398</v>
-      </c>
-      <c r="D96" t="s">
+      <c r="B120" t="s">
+        <v>369</v>
+      </c>
+      <c r="C120" t="s">
+        <v>369</v>
+      </c>
+      <c r="D120" t="s">
+        <v>369</v>
+      </c>
+      <c r="E120" t="s">
+        <v>369</v>
+      </c>
+      <c r="F120" t="s">
         <v>402</v>
       </c>
-      <c r="E96" t="s">
-        <v>399</v>
-      </c>
-      <c r="F96" t="s">
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="98" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
+      <c r="B122" t="s">
+        <v>369</v>
+      </c>
+      <c r="C122" t="s">
+        <v>369</v>
+      </c>
+      <c r="D122" t="s">
+        <v>369</v>
+      </c>
+      <c r="E122" t="s">
+        <v>369</v>
+      </c>
+      <c r="F122" t="s">
         <v>404</v>
       </c>
-      <c r="B98" t="s">
-        <v>397</v>
-      </c>
-      <c r="C98" t="s">
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
         <v>405</v>
       </c>
-      <c r="D98" t="s">
-        <v>402</v>
-      </c>
-      <c r="E98" t="s">
+      <c r="B124" t="s">
+        <v>369</v>
+      </c>
+      <c r="C124" t="s">
+        <v>369</v>
+      </c>
+      <c r="D124" t="s">
+        <v>369</v>
+      </c>
+      <c r="E124" t="s">
+        <v>369</v>
+      </c>
+      <c r="F124" t="s">
         <v>406</v>
       </c>
-      <c r="F98" t="s">
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="100" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
+      <c r="B126" t="s">
+        <v>369</v>
+      </c>
+      <c r="C126" t="s">
+        <v>369</v>
+      </c>
+      <c r="D126" t="s">
+        <v>369</v>
+      </c>
+      <c r="E126" t="s">
+        <v>369</v>
+      </c>
+      <c r="F126" t="s">
         <v>408</v>
       </c>
-      <c r="B100" t="s">
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
         <v>409</v>
       </c>
-      <c r="C100" t="s">
+      <c r="B128" t="s">
+        <v>369</v>
+      </c>
+      <c r="C128" t="s">
+        <v>369</v>
+      </c>
+      <c r="D128" t="s">
+        <v>369</v>
+      </c>
+      <c r="E128" t="s">
+        <v>369</v>
+      </c>
+      <c r="F128" t="s">
         <v>410</v>
       </c>
-      <c r="D100" t="s">
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
         <v>411</v>
       </c>
-      <c r="E100" t="s">
+      <c r="B130" t="s">
+        <v>369</v>
+      </c>
+      <c r="C130" t="s">
+        <v>369</v>
+      </c>
+      <c r="D130" t="s">
+        <v>369</v>
+      </c>
+      <c r="E130" t="s">
+        <v>369</v>
+      </c>
+      <c r="F130" t="s">
         <v>412</v>
       </c>
-      <c r="F100" t="s">
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="102" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
+      <c r="B132" t="s">
+        <v>369</v>
+      </c>
+      <c r="C132" t="s">
+        <v>369</v>
+      </c>
+      <c r="D132" t="s">
+        <v>369</v>
+      </c>
+      <c r="E132" t="s">
+        <v>369</v>
+      </c>
+      <c r="F132" t="s">
         <v>414</v>
       </c>
-      <c r="B102" t="s">
-        <v>409</v>
-      </c>
-      <c r="C102" t="s">
-        <v>410</v>
-      </c>
-      <c r="D102" t="s">
-        <v>411</v>
-      </c>
-      <c r="E102" t="s">
-        <v>412</v>
-      </c>
-      <c r="F102" t="s">
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="104" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
+      <c r="B134" t="s">
+        <v>369</v>
+      </c>
+      <c r="C134" t="s">
+        <v>369</v>
+      </c>
+      <c r="D134" t="s">
+        <v>369</v>
+      </c>
+      <c r="E134" t="s">
+        <v>369</v>
+      </c>
+      <c r="F134" t="s">
         <v>416</v>
       </c>
-      <c r="B104" t="s">
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
         <v>417</v>
       </c>
-      <c r="C104" t="s">
-        <v>417</v>
-      </c>
-      <c r="D104" t="s">
-        <v>417</v>
-      </c>
-      <c r="E104" t="s">
-        <v>417</v>
-      </c>
-      <c r="F104" t="s">
+      <c r="B136" t="s">
+        <v>369</v>
+      </c>
+      <c r="C136" t="s">
+        <v>369</v>
+      </c>
+      <c r="D136" t="s">
+        <v>369</v>
+      </c>
+      <c r="E136" t="s">
+        <v>369</v>
+      </c>
+      <c r="F136" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
         <v>419</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B138" t="s">
+        <v>369</v>
+      </c>
+      <c r="C138" t="s">
+        <v>369</v>
+      </c>
+      <c r="D138" t="s">
+        <v>369</v>
+      </c>
+      <c r="E138" t="s">
+        <v>369</v>
+      </c>
+      <c r="F138" t="s">
         <v>420</v>
       </c>
-      <c r="C106" t="s">
-        <v>410</v>
-      </c>
-      <c r="D106" t="s">
-        <v>411</v>
-      </c>
-      <c r="E106" t="s">
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
         <v>421</v>
       </c>
-      <c r="F106" t="s">
+      <c r="B140" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="108" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
+      <c r="C140" t="s">
         <v>423</v>
       </c>
-      <c r="B108" t="s">
-        <v>417</v>
-      </c>
-      <c r="C108" t="s">
-        <v>417</v>
-      </c>
-      <c r="D108" t="s">
-        <v>417</v>
-      </c>
-      <c r="E108" t="s">
-        <v>417</v>
-      </c>
-      <c r="F108" t="s">
+      <c r="D140" t="s">
+        <v>423</v>
+      </c>
+      <c r="E140" t="s">
+        <v>423</v>
+      </c>
+      <c r="F140" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
         <v>425</v>
       </c>
-      <c r="B110" t="s">
-        <v>417</v>
-      </c>
-      <c r="C110" t="s">
-        <v>417</v>
-      </c>
-      <c r="D110" t="s">
-        <v>417</v>
-      </c>
-      <c r="E110" t="s">
-        <v>417</v>
-      </c>
-      <c r="F110" t="s">
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>319</v>
+      </c>
+      <c r="B144" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="112" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
+      <c r="C144" t="s">
         <v>427</v>
       </c>
-      <c r="B112" t="s">
-        <v>417</v>
-      </c>
-      <c r="C112" t="s">
-        <v>417</v>
-      </c>
-      <c r="D112" t="s">
-        <v>417</v>
-      </c>
-      <c r="E112" t="s">
-        <v>417</v>
-      </c>
-      <c r="F112" t="s">
+      <c r="D144" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="114" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
+      <c r="E144" t="s">
         <v>429</v>
       </c>
-      <c r="B114" t="s">
-        <v>417</v>
-      </c>
-      <c r="C114" t="s">
-        <v>417</v>
-      </c>
-      <c r="D114" t="s">
-        <v>417</v>
-      </c>
-      <c r="E114" t="s">
-        <v>417</v>
-      </c>
-      <c r="F114" t="s">
+      <c r="F144" t="s">
         <v>430</v>
       </c>
-    </row>
-    <row r="116" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
+      <c r="G144" t="s">
         <v>431</v>
       </c>
-      <c r="B116" t="s">
+      <c r="H144" t="s">
         <v>432</v>
       </c>
-      <c r="C116" t="s">
-        <v>406</v>
-      </c>
-      <c r="D116" t="s">
+      <c r="I144" t="s">
         <v>433</v>
       </c>
-      <c r="E116" t="s">
-        <v>434</v>
-      </c>
-      <c r="F116" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
-        <v>436</v>
-      </c>
-      <c r="B118" t="s">
-        <v>406</v>
-      </c>
-      <c r="C118" t="s">
-        <v>406</v>
-      </c>
-      <c r="D118" t="s">
-        <v>433</v>
-      </c>
-      <c r="E118" t="s">
-        <v>406</v>
-      </c>
-      <c r="F118" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A120" t="s">
-        <v>438</v>
-      </c>
-      <c r="B120" t="s">
-        <v>406</v>
-      </c>
-      <c r="C120" t="s">
-        <v>406</v>
-      </c>
-      <c r="D120" t="s">
-        <v>406</v>
-      </c>
-      <c r="E120" t="s">
-        <v>406</v>
-      </c>
-      <c r="F120" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A122" t="s">
-        <v>440</v>
-      </c>
-      <c r="B122" t="s">
-        <v>406</v>
-      </c>
-      <c r="C122" t="s">
-        <v>406</v>
-      </c>
-      <c r="D122" t="s">
-        <v>406</v>
-      </c>
-      <c r="E122" t="s">
-        <v>406</v>
-      </c>
-      <c r="F122" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A124" t="s">
-        <v>442</v>
-      </c>
-      <c r="B124" t="s">
-        <v>406</v>
-      </c>
-      <c r="C124" t="s">
-        <v>406</v>
-      </c>
-      <c r="D124" t="s">
-        <v>406</v>
-      </c>
-      <c r="E124" t="s">
-        <v>406</v>
-      </c>
-      <c r="F124" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A126" t="s">
-        <v>444</v>
-      </c>
-      <c r="B126" t="s">
-        <v>406</v>
-      </c>
-      <c r="C126" t="s">
-        <v>406</v>
-      </c>
-      <c r="D126" t="s">
-        <v>406</v>
-      </c>
-      <c r="E126" t="s">
-        <v>406</v>
-      </c>
-      <c r="F126" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A128" t="s">
-        <v>446</v>
-      </c>
-      <c r="B128" t="s">
-        <v>406</v>
-      </c>
-      <c r="C128" t="s">
-        <v>406</v>
-      </c>
-      <c r="D128" t="s">
-        <v>406</v>
-      </c>
-      <c r="E128" t="s">
-        <v>406</v>
-      </c>
-      <c r="F128" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="130" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A130" t="s">
-        <v>448</v>
-      </c>
-      <c r="B130" t="s">
-        <v>406</v>
-      </c>
-      <c r="C130" t="s">
-        <v>406</v>
-      </c>
-      <c r="D130" t="s">
-        <v>406</v>
-      </c>
-      <c r="E130" t="s">
-        <v>406</v>
-      </c>
-      <c r="F130" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A132" t="s">
-        <v>450</v>
-      </c>
-      <c r="B132" t="s">
-        <v>406</v>
-      </c>
-      <c r="C132" t="s">
-        <v>406</v>
-      </c>
-      <c r="D132" t="s">
-        <v>406</v>
-      </c>
-      <c r="E132" t="s">
-        <v>406</v>
-      </c>
-      <c r="F132" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="134" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A134" t="s">
-        <v>452</v>
-      </c>
-      <c r="B134" t="s">
-        <v>406</v>
-      </c>
-      <c r="C134" t="s">
-        <v>406</v>
-      </c>
-      <c r="D134" t="s">
-        <v>406</v>
-      </c>
-      <c r="E134" t="s">
-        <v>406</v>
-      </c>
-      <c r="F134" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="136" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A136" t="s">
-        <v>454</v>
-      </c>
-      <c r="B136" t="s">
-        <v>406</v>
-      </c>
-      <c r="C136" t="s">
-        <v>406</v>
-      </c>
-      <c r="D136" t="s">
-        <v>406</v>
-      </c>
-      <c r="E136" t="s">
-        <v>406</v>
-      </c>
-      <c r="F136" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="138" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A138" t="s">
-        <v>456</v>
-      </c>
-      <c r="B138" t="s">
-        <v>406</v>
-      </c>
-      <c r="C138" t="s">
-        <v>406</v>
-      </c>
-      <c r="D138" t="s">
-        <v>406</v>
-      </c>
-      <c r="E138" t="s">
-        <v>406</v>
-      </c>
-      <c r="F138" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="140" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A140" t="s">
-        <v>458</v>
-      </c>
-      <c r="B140" t="s">
-        <v>459</v>
-      </c>
-      <c r="C140" t="s">
-        <v>460</v>
-      </c>
-      <c r="D140" t="s">
-        <v>460</v>
-      </c>
-      <c r="E140" t="s">
-        <v>460</v>
-      </c>
-      <c r="F140" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="143" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A143" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="144" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A144" t="s">
-        <v>356</v>
-      </c>
-      <c r="B144" t="s">
-        <v>463</v>
-      </c>
-      <c r="C144" t="s">
-        <v>464</v>
-      </c>
-      <c r="D144" t="s">
-        <v>465</v>
-      </c>
-      <c r="E144" t="s">
-        <v>466</v>
-      </c>
-      <c r="F144" t="s">
-        <v>467</v>
-      </c>
-      <c r="G144" t="s">
-        <v>468</v>
-      </c>
-      <c r="H144" t="s">
-        <v>469</v>
-      </c>
-      <c r="I144" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="146" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>1</v>
       </c>
@@ -6955,7 +7488,7 @@
         <v>487500</v>
       </c>
     </row>
-    <row r="147" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>2</v>
       </c>
@@ -6969,22 +7502,22 @@
         <v>1000000</v>
       </c>
       <c r="E147" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="F147" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="G147" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="H147" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="I147">
         <v>306559</v>
       </c>
     </row>
-    <row r="148" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>3</v>
       </c>
@@ -6998,22 +7531,22 @@
         <v>550000</v>
       </c>
       <c r="E148" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="F148" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="G148" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="H148" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="I148">
         <v>222385</v>
       </c>
     </row>
-    <row r="149" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>4</v>
       </c>
@@ -7027,22 +7560,22 @@
         <v>350000</v>
       </c>
       <c r="E149" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="F149" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="G149" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="H149" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="I149">
         <v>172033</v>
       </c>
     </row>
-    <row r="150" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>5</v>
       </c>
@@ -7056,22 +7589,22 @@
         <v>260000</v>
       </c>
       <c r="E150" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="F150" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="G150" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="H150" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="I150">
         <v>138467</v>
       </c>
     </row>
-    <row r="151" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>6</v>
       </c>
@@ -7085,22 +7618,22 @@
         <v>195000</v>
       </c>
       <c r="E151" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="F151" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="G151" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="H151" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="I151">
         <v>113291</v>
       </c>
     </row>
-    <row r="152" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>7</v>
       </c>
@@ -7114,22 +7647,22 @@
         <v>155000</v>
       </c>
       <c r="E152" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="F152" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="G152" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="H152" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="I152">
         <v>94829</v>
       </c>
     </row>
-    <row r="153" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>8</v>
       </c>
@@ -7143,22 +7676,22 @@
         <v>136000</v>
       </c>
       <c r="E153" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="F153" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="G153" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="H153" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="I153">
         <v>83081</v>
       </c>
     </row>
-    <row r="154" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>9</v>
       </c>
@@ -7172,22 +7705,22 @@
         <v>120000</v>
       </c>
       <c r="E154" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="F154" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="G154" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="H154" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="I154">
         <v>74689</v>
       </c>
     </row>
-    <row r="155" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>10</v>
       </c>
@@ -7201,22 +7734,22 @@
         <v>113500</v>
       </c>
       <c r="E155" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="F155" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="G155" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="H155" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="I155">
         <v>67975</v>
       </c>
     </row>
-    <row r="156" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>11</v>
       </c>
@@ -7230,88 +7763,88 @@
         <v>107000</v>
       </c>
       <c r="E156" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="F156" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="G156" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="H156" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="I156">
         <v>62939</v>
       </c>
     </row>
-    <row r="157" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>472</v>
+        <v>435</v>
       </c>
       <c r="B157" t="s">
-        <v>473</v>
+        <v>436</v>
       </c>
       <c r="C157" t="s">
-        <v>474</v>
+        <v>437</v>
       </c>
       <c r="D157" t="s">
-        <v>474</v>
+        <v>437</v>
       </c>
       <c r="E157" t="s">
-        <v>474</v>
+        <v>437</v>
       </c>
       <c r="F157" t="s">
-        <v>474</v>
+        <v>437</v>
       </c>
       <c r="G157" t="s">
-        <v>474</v>
+        <v>437</v>
       </c>
       <c r="H157" t="s">
-        <v>474</v>
+        <v>437</v>
       </c>
       <c r="I157" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="159" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="160" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>356</v>
+        <v>319</v>
       </c>
       <c r="B160" t="s">
-        <v>476</v>
+        <v>439</v>
       </c>
       <c r="C160" t="s">
-        <v>477</v>
+        <v>440</v>
       </c>
       <c r="D160" t="s">
-        <v>478</v>
+        <v>441</v>
       </c>
       <c r="E160" t="s">
-        <v>479</v>
+        <v>442</v>
       </c>
       <c r="F160" t="s">
-        <v>480</v>
+        <v>443</v>
       </c>
       <c r="G160" t="s">
-        <v>481</v>
+        <v>444</v>
       </c>
       <c r="H160" t="s">
-        <v>482</v>
+        <v>445</v>
       </c>
       <c r="I160" t="s">
-        <v>483</v>
+        <v>446</v>
       </c>
       <c r="J160" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="161" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>1</v>
       </c>
@@ -7343,292 +7876,292 @@
         <v>3600000</v>
       </c>
     </row>
-    <row r="162" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>2</v>
       </c>
       <c r="B162" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="C162" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="D162" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="E162" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="F162" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="G162" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="H162" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="I162" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="J162" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="163" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>3</v>
       </c>
       <c r="B163" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="C163" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="D163" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="E163" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="F163" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="G163" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="H163" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="I163" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="J163" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="164" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>4</v>
       </c>
       <c r="B164" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="C164" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="D164" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="E164" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="F164" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="G164" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="H164" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="I164" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="J164" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="165" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>5</v>
       </c>
       <c r="B165" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="C165" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="D165" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="E165" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="F165" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="G165" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="H165" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="I165" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="J165" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="166" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>6</v>
       </c>
       <c r="B166" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="C166" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="D166" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="E166" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="F166" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="G166" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="H166" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="I166" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="J166" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="167" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>7</v>
       </c>
       <c r="B167" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="C167" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="D167" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="E167" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="F167" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="G167" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="H167" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="I167" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="J167" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="168" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>8</v>
       </c>
       <c r="B168" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="C168" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="D168" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="E168" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="F168" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="G168" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="H168" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="I168" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="J168" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="169" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>9</v>
       </c>
       <c r="B169" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="C169" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="D169" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="E169" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="F169" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="G169" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="H169" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="I169" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="J169" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="170" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>10</v>
       </c>
       <c r="B170" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="C170" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="D170" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="E170" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="F170" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="G170" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="H170" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="I170" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="J170" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
     </row>
   </sheetData>
@@ -7642,26 +8175,26 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>488</v>
+        <v>451</v>
       </c>
     </row>
   </sheetData>
@@ -7673,23 +8206,1053 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D61C8FA1-4A2C-4E90-9135-F9A930735BCC}">
+  <dimension ref="A1:G32"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>471</v>
+      </c>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D3" s="7">
+        <v>50000</v>
+      </c>
+      <c r="E3" s="7">
+        <v>60000</v>
+      </c>
+      <c r="F3" s="7">
+        <v>70000</v>
+      </c>
+      <c r="G3" s="7">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="D4" s="7">
+        <v>30000</v>
+      </c>
+      <c r="E4" s="7">
+        <v>40000</v>
+      </c>
+      <c r="F4" s="7">
+        <v>50000</v>
+      </c>
+      <c r="G4" s="7">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="D5" s="7">
+        <v>25000</v>
+      </c>
+      <c r="E5" s="7">
+        <v>35000</v>
+      </c>
+      <c r="F5" s="7">
+        <v>40000</v>
+      </c>
+      <c r="G5" s="7">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
+        <v>4</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6" t="s">
+        <v>483</v>
+      </c>
+      <c r="D6" s="7">
+        <v>20000</v>
+      </c>
+      <c r="E6" s="7">
+        <v>30000</v>
+      </c>
+      <c r="F6" s="7">
+        <v>35000</v>
+      </c>
+      <c r="G6" s="7">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
+        <v>5</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="D7" s="7">
+        <v>20000</v>
+      </c>
+      <c r="E7" s="7">
+        <v>25000</v>
+      </c>
+      <c r="F7" s="7">
+        <v>30000</v>
+      </c>
+      <c r="G7" s="7">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
+        <v>6</v>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D8" s="7">
+        <v>15000</v>
+      </c>
+      <c r="E8" s="7">
+        <v>20000</v>
+      </c>
+      <c r="F8" s="7">
+        <v>25000</v>
+      </c>
+      <c r="G8" s="7">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
+        <v>7</v>
+      </c>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="D9" s="7">
+        <v>15000</v>
+      </c>
+      <c r="E9" s="7">
+        <v>15000</v>
+      </c>
+      <c r="F9" s="7">
+        <v>20000</v>
+      </c>
+      <c r="G9" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
+        <v>8</v>
+      </c>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="D10" s="7">
+        <v>15000</v>
+      </c>
+      <c r="E10" s="7">
+        <v>15000</v>
+      </c>
+      <c r="F10" s="7">
+        <v>20000</v>
+      </c>
+      <c r="G10" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>488</v>
+      </c>
+      <c r="C12" s="6"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>489</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>490</v>
+      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>492</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
+        <v>3</v>
+      </c>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
+        <v>4</v>
+      </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
+        <v>5</v>
+      </c>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6" t="s">
+        <v>494</v>
+      </c>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
+        <v>6</v>
+      </c>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6" t="s">
+        <v>495</v>
+      </c>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
+        <v>7</v>
+      </c>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6" t="s">
+        <v>496</v>
+      </c>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="5">
+        <v>8</v>
+      </c>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>498</v>
+      </c>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="2"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>500</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="G24" s="2"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" s="7">
+        <v>50000</v>
+      </c>
+      <c r="C25" s="7">
+        <v>50000</v>
+      </c>
+      <c r="D25" s="7">
+        <v>30000</v>
+      </c>
+      <c r="E25" s="7">
+        <v>25000</v>
+      </c>
+      <c r="F25" s="7">
+        <v>20000</v>
+      </c>
+      <c r="G25" s="2"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="B26" s="7">
+        <v>30000</v>
+      </c>
+      <c r="C26" s="7">
+        <v>40000</v>
+      </c>
+      <c r="D26" s="7">
+        <v>20000</v>
+      </c>
+      <c r="E26" s="7">
+        <v>15000</v>
+      </c>
+      <c r="F26" s="7">
+        <v>15000</v>
+      </c>
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="5">
+        <v>3</v>
+      </c>
+      <c r="B27" s="7">
+        <v>25000</v>
+      </c>
+      <c r="C27" s="7">
+        <v>30000</v>
+      </c>
+      <c r="D27" s="7">
+        <v>15000</v>
+      </c>
+      <c r="E27" s="7">
+        <v>12000</v>
+      </c>
+      <c r="F27" s="7">
+        <v>10000</v>
+      </c>
+      <c r="G27" s="2"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="5">
+        <v>4</v>
+      </c>
+      <c r="B28" s="7">
+        <v>20000</v>
+      </c>
+      <c r="C28" s="7">
+        <v>25000</v>
+      </c>
+      <c r="D28" s="7">
+        <v>10000</v>
+      </c>
+      <c r="E28" s="7">
+        <v>10000</v>
+      </c>
+      <c r="F28" s="7">
+        <v>8000</v>
+      </c>
+      <c r="G28" s="2"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="5">
+        <v>5</v>
+      </c>
+      <c r="B29" s="7">
+        <v>15000</v>
+      </c>
+      <c r="C29" s="7">
+        <v>20000</v>
+      </c>
+      <c r="D29" s="7">
+        <v>8000</v>
+      </c>
+      <c r="E29" s="7">
+        <v>8000</v>
+      </c>
+      <c r="F29" s="7">
+        <v>7000</v>
+      </c>
+      <c r="G29" s="2"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="5">
+        <v>6</v>
+      </c>
+      <c r="B30" s="7">
+        <v>10000</v>
+      </c>
+      <c r="C30" s="7">
+        <v>15000</v>
+      </c>
+      <c r="D30" s="7">
+        <v>5000</v>
+      </c>
+      <c r="E30" s="7">
+        <v>5000</v>
+      </c>
+      <c r="F30" s="7">
+        <v>5000</v>
+      </c>
+      <c r="G30" s="2"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="5">
+        <v>7</v>
+      </c>
+      <c r="B31" s="7">
+        <v>5000</v>
+      </c>
+      <c r="C31" s="7">
+        <v>10000</v>
+      </c>
+      <c r="D31" s="7">
+        <v>5000</v>
+      </c>
+      <c r="E31" s="7">
+        <v>5000</v>
+      </c>
+      <c r="F31" s="7">
+        <v>5000</v>
+      </c>
+      <c r="G31" s="2"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="5">
+        <v>8</v>
+      </c>
+      <c r="B32" s="7">
+        <v>5000</v>
+      </c>
+      <c r="C32" s="7">
+        <v>10000</v>
+      </c>
+      <c r="D32" s="7">
+        <v>5000</v>
+      </c>
+      <c r="E32" s="7">
+        <v>5000</v>
+      </c>
+      <c r="F32" s="7">
+        <v>5000</v>
+      </c>
+      <c r="G32" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB5F8C4D-0CDF-4A96-8030-E746883E61F3}">
+  <dimension ref="A1:K23"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="14.09765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.3984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.09765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.8984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.59765625" customWidth="1"/>
+    <col min="9" max="9" width="11.796875" customWidth="1"/>
+    <col min="10" max="10" width="11.69921875" customWidth="1"/>
+    <col min="11" max="11" width="13.3984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
+        <v>504</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>506</v>
+      </c>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B2" s="11" t="s">
+        <v>507</v>
+      </c>
+      <c r="C2" s="12">
+        <v>50000000</v>
+      </c>
+      <c r="D2" s="13">
+        <v>5000000</v>
+      </c>
+      <c r="F2" s="10"/>
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="15"/>
+      <c r="B3" s="11" t="s">
+        <v>508</v>
+      </c>
+      <c r="C3" s="12">
+        <v>33000000</v>
+      </c>
+      <c r="D3" s="13">
+        <v>4000000</v>
+      </c>
+      <c r="F3" s="10"/>
+      <c r="G3" s="14"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="15"/>
+      <c r="B4" s="11" t="s">
+        <v>509</v>
+      </c>
+      <c r="C4" s="12">
+        <v>29000000</v>
+      </c>
+      <c r="D4" s="13">
+        <v>2500000</v>
+      </c>
+      <c r="F4" s="10"/>
+      <c r="G4" s="14"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="15"/>
+      <c r="B5" s="11" t="s">
+        <v>510</v>
+      </c>
+      <c r="C5" s="12">
+        <v>27000000</v>
+      </c>
+      <c r="D5" s="13">
+        <v>2000000</v>
+      </c>
+      <c r="F5" s="10"/>
+      <c r="G5" s="14"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="15"/>
+      <c r="B6" s="11" t="s">
+        <v>511</v>
+      </c>
+      <c r="C6" s="12">
+        <v>19000000</v>
+      </c>
+      <c r="D6" s="13">
+        <v>1500000</v>
+      </c>
+      <c r="F6" s="10"/>
+      <c r="G6" s="14"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="15"/>
+      <c r="B7" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="C7" s="12">
+        <v>19000000</v>
+      </c>
+      <c r="D7" s="13">
+        <v>1000000</v>
+      </c>
+      <c r="F7" s="10"/>
+      <c r="G7" s="14"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="15"/>
+      <c r="B8" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="C8" s="12">
+        <v>19000000</v>
+      </c>
+      <c r="D8" s="13">
+        <v>500000</v>
+      </c>
+      <c r="F8" s="10"/>
+      <c r="G8" s="14"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="15"/>
+      <c r="B9" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="C9" s="12">
+        <v>19000000</v>
+      </c>
+      <c r="D9" s="16"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="15"/>
+      <c r="B10" s="11" t="s">
+        <v>512</v>
+      </c>
+      <c r="C10" s="12">
+        <v>13000000</v>
+      </c>
+      <c r="D10" s="16"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="15"/>
+      <c r="B11" s="11" t="s">
+        <v>513</v>
+      </c>
+      <c r="C11" s="12">
+        <v>11000000</v>
+      </c>
+      <c r="D11" s="16"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="15"/>
+      <c r="B12" s="11" t="s">
+        <v>514</v>
+      </c>
+      <c r="C12" s="12">
+        <v>10500000</v>
+      </c>
+      <c r="D12" s="16"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B13" s="11" t="s">
+        <v>515</v>
+      </c>
+      <c r="C13" s="12">
+        <v>2000000</v>
+      </c>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+    </row>
+    <row r="14" spans="1:11" ht="18" x14ac:dyDescent="0.3">
+      <c r="A14" s="18"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+    </row>
+    <row r="15" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="22" t="s">
+        <v>516</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>518</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="F15" s="24" t="s">
+        <v>520</v>
+      </c>
+      <c r="G15" s="25" t="s">
+        <v>521</v>
+      </c>
+      <c r="H15" s="25" t="s">
+        <v>522</v>
+      </c>
+      <c r="I15" s="25" t="s">
+        <v>523</v>
+      </c>
+      <c r="J15" s="26" t="s">
+        <v>524</v>
+      </c>
+      <c r="K15" s="26" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="27"/>
+      <c r="B16" s="11" t="s">
+        <v>507</v>
+      </c>
+      <c r="C16" s="12">
+        <v>6000000</v>
+      </c>
+      <c r="D16" s="28">
+        <v>8000000</v>
+      </c>
+      <c r="E16" s="12">
+        <v>16000000</v>
+      </c>
+      <c r="F16" s="29">
+        <v>6000000</v>
+      </c>
+      <c r="G16" s="13">
+        <v>7000000</v>
+      </c>
+      <c r="H16" s="30">
+        <v>8600000</v>
+      </c>
+      <c r="I16" s="31">
+        <v>18000000</v>
+      </c>
+      <c r="J16" s="30">
+        <v>25000000</v>
+      </c>
+      <c r="K16" s="13">
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="27"/>
+      <c r="B17" s="11" t="s">
+        <v>508</v>
+      </c>
+      <c r="C17" s="12">
+        <v>2000000</v>
+      </c>
+      <c r="D17" s="28">
+        <v>5000000</v>
+      </c>
+      <c r="E17" s="12">
+        <v>7000000</v>
+      </c>
+      <c r="F17" s="29">
+        <v>2000000</v>
+      </c>
+      <c r="G17" s="13">
+        <v>4000000</v>
+      </c>
+      <c r="H17" s="30">
+        <v>4600000</v>
+      </c>
+      <c r="I17" s="31">
+        <v>7000000</v>
+      </c>
+      <c r="J17" s="30">
+        <v>18500000</v>
+      </c>
+      <c r="K17" s="13">
+        <v>3000000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="27"/>
+      <c r="B18" s="11" t="s">
+        <v>526</v>
+      </c>
+      <c r="C18" s="12">
+        <v>1200000</v>
+      </c>
+      <c r="D18" s="28">
+        <v>4000000</v>
+      </c>
+      <c r="E18" s="32"/>
+      <c r="F18" s="29">
+        <v>1200000</v>
+      </c>
+      <c r="G18" s="13">
+        <v>2500000</v>
+      </c>
+      <c r="H18" s="30">
+        <v>2800000</v>
+      </c>
+      <c r="I18" s="31">
+        <v>2300000</v>
+      </c>
+      <c r="J18" s="30">
+        <v>15000000</v>
+      </c>
+      <c r="K18" s="13">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="27"/>
+      <c r="B19" s="11" t="s">
+        <v>527</v>
+      </c>
+      <c r="C19" s="12">
+        <v>900000</v>
+      </c>
+      <c r="D19" s="28">
+        <v>2500000</v>
+      </c>
+      <c r="E19" s="32"/>
+      <c r="F19" s="33" t="s">
+        <v>528</v>
+      </c>
+      <c r="G19" s="13">
+        <v>1300000</v>
+      </c>
+      <c r="H19" s="30">
+        <v>1800000</v>
+      </c>
+      <c r="I19" s="31">
+        <v>1700000</v>
+      </c>
+      <c r="J19" s="30">
+        <v>12500000</v>
+      </c>
+      <c r="K19" s="13"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="27"/>
+      <c r="B20" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="34"/>
+      <c r="D20" s="28">
+        <v>1500000</v>
+      </c>
+      <c r="E20" s="32"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="30">
+        <v>1200000</v>
+      </c>
+      <c r="I20" s="31">
+        <v>1250000</v>
+      </c>
+      <c r="J20" s="30">
+        <v>11000000</v>
+      </c>
+      <c r="K20" s="35"/>
+    </row>
+    <row r="21" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B21" s="36" t="s">
+        <v>529</v>
+      </c>
+      <c r="C21" s="32"/>
+      <c r="D21" s="37">
+        <v>1000000</v>
+      </c>
+      <c r="E21" s="32"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="38">
+        <v>630000</v>
+      </c>
+      <c r="I21" s="31">
+        <v>330000</v>
+      </c>
+      <c r="J21" s="30">
+        <v>2100000</v>
+      </c>
+      <c r="K21" s="35"/>
+    </row>
+    <row r="22" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B22" s="36" t="s">
+        <v>530</v>
+      </c>
+      <c r="C22" s="32"/>
+      <c r="D22" s="37">
+        <v>500000</v>
+      </c>
+      <c r="E22" s="32"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="30">
+        <v>210000</v>
+      </c>
+      <c r="I22" s="32"/>
+      <c r="J22" s="30">
+        <v>700000</v>
+      </c>
+      <c r="K22" s="35"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="27"/>
+      <c r="B23" s="11" t="s">
+        <v>515</v>
+      </c>
+      <c r="C23" s="32"/>
+      <c r="D23" s="37">
+        <v>9250000</v>
+      </c>
+      <c r="E23" s="32"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="31">
+        <v>3000000</v>
+      </c>
+      <c r="J23" s="30">
+        <v>18620000</v>
+      </c>
+      <c r="K23" s="13">
+        <v>200000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>491</v>
+        <v>454</v>
       </c>
     </row>
   </sheetData>
